--- a/docentes/Avila Coronado Julieta - Estadisticos 20211.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -82,94 +82,73 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>ZAVALETA</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
   </si>
   <si>
     <t>CERON</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>MARIAN</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
+    <t>VANELY JUDITH</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
   </si>
   <si>
     <t>ISRAEL</t>
   </si>
   <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>ARLET</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
     <t>YAMILE</t>
-  </si>
-  <si>
-    <t>ARLET</t>
-  </si>
-  <si>
-    <t>MARIA ASUNCION</t>
-  </si>
-  <si>
-    <t>JOSELIN GUADALUPE</t>
   </si>
 </sst>
 </file>
@@ -570,19 +549,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>55.56</v>
+        <v>80.56</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -596,19 +575,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -622,19 +601,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -648,19 +627,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -674,19 +653,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>59.38</v>
+        <v>87.5</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -700,19 +679,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -765,16 +744,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80.56</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -788,16 +770,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.62</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -811,16 +796,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -834,16 +822,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>77.78</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -857,16 +848,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H6">
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -880,16 +874,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>68.56999999999999</v>
+      </c>
+      <c r="H7">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -942,19 +939,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>55.56</v>
+        <v>80.56</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -968,19 +965,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -994,19 +991,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1020,19 +1017,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1046,19 +1043,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>59.38</v>
+        <v>87.5</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1072,19 +1069,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1094,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1126,154 +1123,154 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920002</v>
+        <v>20330051920220</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920336</v>
+        <v>20330051920174</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920263</v>
+        <v>20330051920284</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920168</v>
+        <v>20330051920285</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920184</v>
+        <v>20330051920297</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920040</v>
+        <v>20330051920252</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920284</v>
+        <v>20330051920286</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1282,7 +1279,7 @@
         <v>14</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1290,13 +1287,13 @@
         <v>20330051920295</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1305,76 +1302,7 @@
         <v>14</v>
       </c>
       <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920252</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920053</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920313</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20211.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -85,42 +85,48 @@
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
     <t>NAMORADO</t>
   </si>
   <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>ALFONSO</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>OSORIO</t>
   </si>
   <si>
@@ -130,19 +136,22 @@
     <t>VANELY JUDITH</t>
   </si>
   <si>
+    <t>CESAR</t>
+  </si>
+  <si>
     <t>LUZ ESTRELLA</t>
   </si>
   <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>ARLET</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>ARLET</t>
   </si>
   <si>
     <t>AMERICA MICHELLE</t>
@@ -1091,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1129,10 +1138,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,48 +1155,48 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920174</v>
+        <v>20330051920340</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920284</v>
+        <v>20330051920174</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1198,10 +1207,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1221,10 +1230,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1233,7 +1242,7 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1244,10 +1253,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1261,16 +1270,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920286</v>
+        <v>20330051920284</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1279,21 +1288,21 @@
         <v>14</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920295</v>
+        <v>20330051920286</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1303,6 +1312,29 @@
       </c>
       <c r="G9">
         <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920295</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20211.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>ARELLANO</t>
   </si>
   <si>
@@ -106,15 +109,15 @@
     <t>ALFONSO</t>
   </si>
   <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>CUATRA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -131,6 +134,9 @@
   </si>
   <si>
     <t>CERON</t>
+  </si>
+  <si>
+    <t>ANDRES NOEL</t>
   </si>
   <si>
     <t>VANELY JUDITH</t>
@@ -1100,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1132,99 +1138,99 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920220</v>
+        <v>20330051920363</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920340</v>
+        <v>20330051920220</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920174</v>
+        <v>20330051920340</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920285</v>
+        <v>20330051920174</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920297</v>
+        <v>20330051920285</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1233,7 +1239,7 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1247,7 +1253,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920252</v>
+        <v>20330051920297</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1256,21 +1262,21 @@
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920284</v>
+        <v>20330051920252</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1279,13 +1285,13 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1293,7 +1299,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920286</v>
+        <v>20330051920284</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -1302,7 +1308,7 @@
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1311,21 +1317,21 @@
         <v>14</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920295</v>
+        <v>20330051920286</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1334,6 +1340,29 @@
         <v>14</v>
       </c>
       <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920295</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20211.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="67">
   <si>
     <t>Mat</t>
   </si>
@@ -82,88 +82,142 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>VERA</t>
   </si>
   <si>
     <t>ARROYO</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>ANDRES NOEL</t>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>ELELYN IVETH</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>BENY ALEXANDER</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
   </si>
   <si>
     <t>VANELY JUDITH</t>
   </si>
   <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>ARLET</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>YAMILE</t>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
   </si>
 </sst>
 </file>
@@ -957,16 +1011,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>80.56</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -983,16 +1037,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>84.62</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1009,16 +1063,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1044,7 +1098,7 @@
         <v>77.78</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1061,16 +1115,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>87.5</v>
+        <v>81.25</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1087,16 +1141,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>68.56999999999999</v>
+        <v>77.14</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1106,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1138,16 +1192,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920363</v>
+        <v>20330051920013</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1156,50 +1210,50 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920220</v>
+        <v>20330051920034</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920340</v>
+        <v>20330051920244</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1207,45 +1261,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920174</v>
+        <v>20330051920340</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920285</v>
+        <v>20330051920354</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1253,22 +1307,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920297</v>
+        <v>20330051920183</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1276,62 +1330,62 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920252</v>
+        <v>20330051920100</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920284</v>
+        <v>20330051920109</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920286</v>
+        <v>20330051920307</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1345,24 +1399,185 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920295</v>
+        <v>20330051920220</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920337</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920356</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920157</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920052</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
         <v>48</v>
       </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920097</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920366</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920367</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20211.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
   <si>
     <t>Mat</t>
   </si>
@@ -103,6 +103,9 @@
     <t>TELLEZ</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -148,6 +151,9 @@
     <t>VALENCIA</t>
   </si>
   <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
@@ -194,6 +200,9 @@
   </si>
   <si>
     <t>BENY ALEXANDER</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
   </si>
   <si>
     <t>MARIANA</t>
@@ -1160,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1198,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1221,10 +1230,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1244,10 +1253,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1267,10 +1276,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1290,10 +1299,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1313,10 +1322,10 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1336,10 +1345,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1359,10 +1368,10 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1376,16 +1385,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920307</v>
+        <v>20330051920286</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1399,45 +1408,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920220</v>
+        <v>20330051920307</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920337</v>
+        <v>20330051920220</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1445,16 +1454,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920356</v>
+        <v>20330051920337</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1468,22 +1477,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920157</v>
+        <v>20330051920356</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1491,22 +1500,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920052</v>
+        <v>20330051920157</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1514,16 +1523,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920097</v>
+        <v>20330051920052</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1537,16 +1546,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920366</v>
+        <v>20330051920097</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1560,16 +1569,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920367</v>
+        <v>20330051920366</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1578,6 +1587,29 @@
         <v>13</v>
       </c>
       <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920367</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>
